--- a/basedatos_partidas/salida/descompuestos/05.04.01.050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/05.04.01.050.xlsx
@@ -610,7 +610,7 @@
         <v>0.006</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>0.03</v>
